--- a/public/downloads/MontoyaThe2015.xlsx
+++ b/public/downloads/MontoyaThe2015.xlsx
@@ -8,28 +8,30 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="57">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -61,10 +63,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -163,13 +165,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>NH</t>
   </si>
   <si>
-    <t>N</t>
+    <t>H</t>
   </si>
   <si>
-    <t>H</t>
+    <t>N</t>
   </si>
   <si>
     <t>NH2</t>
@@ -664,10 +687,10 @@
         <v>248</v>
       </c>
       <c r="N3" s="5">
-        <v>655.5747041702271</v>
+        <v>655574.7041702271</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03064722098874419</v>
+        <v>30.64722098874419</v>
       </c>
       <c r="P3" s="5">
         <v>21391</v>
@@ -714,10 +737,10 @@
         <v>248</v>
       </c>
       <c r="N4" s="5">
-        <v>1093.849855422974</v>
+        <v>1093849.855422974</v>
       </c>
       <c r="O4" s="4">
-        <v>0.03878487591472445</v>
+        <v>38.78487591472445</v>
       </c>
       <c r="P4" s="5">
         <v>28203</v>
@@ -764,10 +787,10 @@
         <v>248</v>
       </c>
       <c r="N5" s="5">
-        <v>2966.56071138382</v>
+        <v>2966560.71138382</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1258190139699644</v>
+        <v>125.8190139699644</v>
       </c>
       <c r="P5" s="5">
         <v>23578</v>
@@ -814,10 +837,10 @@
         <v>248</v>
       </c>
       <c r="N6" s="5">
-        <v>1861.526801586151</v>
+        <v>1861526.801586151</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08079894099510183</v>
+        <v>80.79894099510183</v>
       </c>
       <c r="P6" s="5">
         <v>23039</v>
@@ -864,10 +887,10 @@
         <v>248</v>
       </c>
       <c r="N7" s="5">
-        <v>2370.727339029312</v>
+        <v>2370727.339029312</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1371869300983341</v>
+        <v>137.1869300983341</v>
       </c>
       <c r="P7" s="5">
         <v>17281</v>
@@ -914,10 +937,10 @@
         <v>248</v>
       </c>
       <c r="N8" s="5">
-        <v>231.2374997138977</v>
+        <v>231237.4997138977</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01010035379199344</v>
+        <v>10.10035379199344</v>
       </c>
       <c r="P8" s="5">
         <v>22894</v>
@@ -964,10 +987,10 @@
         <v>248</v>
       </c>
       <c r="N9" s="5">
-        <v>732.7942359447479</v>
+        <v>732794.2359447479</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02803558940794047</v>
+        <v>28.03558940794047</v>
       </c>
       <c r="P9" s="5">
         <v>26138</v>
@@ -1014,10 +1037,10 @@
         <v>248</v>
       </c>
       <c r="N10" s="5">
-        <v>1647.885342121124</v>
+        <v>1647885.342121124</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08784505262120178</v>
+        <v>87.84505262120177</v>
       </c>
       <c r="P10" s="5">
         <v>18759</v>
@@ -1064,10 +1087,10 @@
         <v>248</v>
       </c>
       <c r="N11" s="5">
-        <v>835.513822555542</v>
+        <v>835513.822555542</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03890815975391367</v>
+        <v>38.90815975391367</v>
       </c>
       <c r="P11" s="5">
         <v>21474</v>
@@ -1114,10 +1137,10 @@
         <v>248</v>
       </c>
       <c r="N12" s="5">
-        <v>361.9780004024506</v>
+        <v>361978.0004024506</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01791438188668962</v>
+        <v>17.91438188668963</v>
       </c>
       <c r="P12" s="5">
         <v>20206</v>
@@ -1164,10 +1187,10 @@
         <v>248</v>
       </c>
       <c r="N13" s="5">
-        <v>1404.903701543808</v>
+        <v>1404903.701543808</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07038595699117274</v>
+        <v>70.38595699117275</v>
       </c>
       <c r="P13" s="5">
         <v>19960</v>
@@ -1214,10 +1237,10 @@
         <v>248</v>
       </c>
       <c r="N14" s="5">
-        <v>2700.647239685059</v>
+        <v>2700647.239685059</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2004190901436036</v>
+        <v>200.4190901436036</v>
       </c>
       <c r="P14" s="5">
         <v>13475</v>
@@ -1264,10 +1287,10 @@
         <v>150</v>
       </c>
       <c r="N15" s="5">
-        <v>2567.930019378662</v>
+        <v>2567930.019378662</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2119103828501949</v>
+        <v>211.9103828501949</v>
       </c>
       <c r="P15" s="5">
         <v>12118</v>
@@ -1314,10 +1337,10 @@
         <v>248</v>
       </c>
       <c r="N16" s="5">
-        <v>1299.178620815277</v>
+        <v>1299178.620815277</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09408883406831381</v>
+        <v>94.08883406831382</v>
       </c>
       <c r="P16" s="5">
         <v>13808</v>
@@ -1345,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1356,9 +1379,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1392,8 +1421,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1415,75 +1452,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3984178886811651</v>
+        <v>0.5520864058356206</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3944315241490254</v>
+        <v>0.4769349366648613</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3771380043926967</v>
+        <v>0.5341009102404671</v>
       </c>
       <c r="E3" s="4">
-        <v>83.94132653061227</v>
+        <v>81.35841836734662</v>
       </c>
       <c r="F3" s="4">
-        <v>90.97152311707711</v>
+        <v>89.43372483221356</v>
       </c>
       <c r="G3" s="5">
         <v>48</v>
       </c>
       <c r="H3" s="5">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4758329141124376</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.194315164748972</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1298965749441935</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3493300456753131</v>
+        <v>0.2601331070877048</v>
       </c>
       <c r="C4" s="4">
-        <v>0.343478845019598</v>
+        <v>0.2436140013744392</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3388189982065262</v>
+        <v>0.2572585760861571</v>
       </c>
       <c r="E4" s="4">
-        <v>83.35649153278308</v>
+        <v>82.32739904472481</v>
       </c>
       <c r="F4" s="4">
-        <v>89.19582083868708</v>
+        <v>90.12780237041231</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -1497,40 +1570,58 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.243394020424158</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08567385012778073</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07556728055072301</v>
+      </c>
+      <c r="R4" s="5">
+        <v>43</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2096603650921032</v>
+        <v>0.3946334729471804</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2042000745025837</v>
+        <v>0.2995955871370625</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2000033499711869</v>
+        <v>0.3630551188633059</v>
       </c>
       <c r="E5" s="4">
-        <v>82.71602257924401</v>
+        <v>82.83687943262461</v>
       </c>
       <c r="F5" s="4">
-        <v>90.11780665429073</v>
+        <v>90.33604645628159</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>3</v>
@@ -1538,40 +1629,58 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2554322134533396</v>
+      </c>
+      <c r="O5" s="5">
+        <v>43</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2344497486249714</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1482721873851913</v>
+      </c>
+      <c r="R5" s="5">
+        <v>43</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4606424419597763</v>
+        <v>0.6483844529519606</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4368765975712264</v>
+        <v>0.6159858620658536</v>
       </c>
       <c r="D6" s="4">
-        <v>0.419752419255657</v>
+        <v>0.5865848125711979</v>
       </c>
       <c r="E6" s="4">
-        <v>83.16553287981938</v>
+        <v>82.96674225245683</v>
       </c>
       <c r="F6" s="4">
-        <v>91.05120556798495</v>
+        <v>90.1807109122537</v>
       </c>
       <c r="G6" s="5">
         <v>45</v>
       </c>
       <c r="H6" s="5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
         <v>1</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
       </c>
       <c r="L6" s="5">
         <v>1</v>
@@ -1579,75 +1688,111 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.6159858620658536</v>
+      </c>
+      <c r="O6" s="5">
+        <v>42</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1683761362303682</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1456902271545656</v>
+      </c>
+      <c r="R6" s="5">
+        <v>42</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
-        <v>0.3285976065704065</v>
+        <v>0.4877421573100326</v>
       </c>
       <c r="C7" s="4">
-        <v>0.2596640541314936</v>
+        <v>0.4031812497024094</v>
       </c>
       <c r="D7" s="4">
-        <v>0.2417247412907506</v>
+        <v>0.4035089983676503</v>
       </c>
       <c r="E7" s="4">
-        <v>77.52705627705642</v>
+        <v>76.81354359925814</v>
       </c>
       <c r="F7" s="4">
-        <v>83.38799064470213</v>
+        <v>82.79896278218374</v>
       </c>
       <c r="G7" s="5">
         <v>44</v>
       </c>
       <c r="H7" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I7" s="5">
         <v>7</v>
       </c>
       <c r="J7" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.4031812497024094</v>
+      </c>
+      <c r="O7" s="5">
+        <v>34</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2274745341778402</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1656374996267651</v>
+      </c>
+      <c r="R7" s="5">
+        <v>34</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
-        <v>0.4152222895613265</v>
+        <v>0.5855863066526477</v>
       </c>
       <c r="C8" s="4">
-        <v>0.4152222895613265</v>
+        <v>0.5634675455134803</v>
       </c>
       <c r="D8" s="4">
-        <v>0.4022171835595413</v>
+        <v>0.5805263087183876</v>
       </c>
       <c r="E8" s="4">
-        <v>82.83913565426171</v>
+        <v>82.52100840336145</v>
       </c>
       <c r="F8" s="4">
-        <v>91.67390446111332</v>
+        <v>90.30201342281914</v>
       </c>
       <c r="G8" s="5">
         <v>17</v>
       </c>
       <c r="H8" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -1661,9 +1806,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.5634675455134803</v>
+      </c>
+      <c r="O8" s="5">
+        <v>16</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2096798430419383</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1992836495216942</v>
+      </c>
+      <c r="R8" s="5">
+        <v>16</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1674,6 +1837,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1681,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1692,9 +1856,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1728,8 +1898,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1751,37 +1929,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6102541603175256</v>
+        <v>0.854716163628047</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5983137379949834</v>
+        <v>0.7852927012475067</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5951757647124383</v>
+        <v>0.8130253372120313</v>
       </c>
       <c r="E3" s="4">
-        <v>81.26488095238089</v>
+        <v>81.15858843537451</v>
       </c>
       <c r="F3" s="4">
-        <v>88.31375838926169</v>
+        <v>89.27875652498163</v>
       </c>
       <c r="G3" s="5">
         <v>48</v>
       </c>
       <c r="H3" s="5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -1790,42 +1986,60 @@
         <v>4</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.8450265093239963</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3608030018556369</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3830327427835485</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4519771537424285</v>
+        <v>0.389984977227257</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4466788524325532</v>
+        <v>0.3707292246939776</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4615801671260098</v>
+        <v>0.3233822575292674</v>
       </c>
       <c r="E4" s="4">
-        <v>83.76103632942589</v>
+        <v>82.18772615429133</v>
       </c>
       <c r="F4" s="4">
-        <v>89.89433100099853</v>
+        <v>87.40325574753797</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -1833,40 +2047,58 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3570389620968748</v>
+      </c>
+      <c r="O4" s="5">
+        <v>40</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1750622924696615</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1806768884707559</v>
+      </c>
+      <c r="R4" s="5">
+        <v>40</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5117008986349001</v>
+        <v>0.4570295425017177</v>
       </c>
       <c r="C5" s="4">
-        <v>0.511893763266775</v>
+        <v>0.3531214953840928</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4751974720627903</v>
+        <v>0.3479338418626124</v>
       </c>
       <c r="E5" s="4">
-        <v>81.4640324214791</v>
+        <v>82.70589086698503</v>
       </c>
       <c r="F5" s="4">
-        <v>86.6792803084391</v>
+        <v>87.19191774953553</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>3</v>
@@ -1874,37 +2106,55 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2543870006858363</v>
+      </c>
+      <c r="O5" s="5">
+        <v>39</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4137592529448363</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3316670238850687</v>
+      </c>
+      <c r="R5" s="5">
+        <v>39</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
-        <v>0.7814285974899192</v>
+        <v>1.165649017479611</v>
       </c>
       <c r="C6" s="4">
-        <v>0.7790792270936027</v>
+        <v>1.065595186329314</v>
       </c>
       <c r="D6" s="4">
-        <v>0.7351825880871143</v>
+        <v>1.064581453257063</v>
       </c>
       <c r="E6" s="4">
-        <v>83.00226757369644</v>
+        <v>80.92970521541973</v>
       </c>
       <c r="F6" s="4">
-        <v>88.77106636838319</v>
+        <v>86.55456127268302</v>
       </c>
       <c r="G6" s="5">
         <v>45</v>
       </c>
       <c r="H6" s="5">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -1913,80 +2163,116 @@
         <v>1</v>
       </c>
       <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-1.142360667648442</v>
+      </c>
+      <c r="O6" s="5">
+        <v>39</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2943358739009098</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3127471431573925</v>
+      </c>
+      <c r="R6" s="5">
+        <v>39</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
-        <v>0.6281664793997771</v>
+        <v>1.179442865772284</v>
       </c>
       <c r="C7" s="4">
-        <v>0.5327197413329954</v>
+        <v>1.024270833361865</v>
       </c>
       <c r="D7" s="4">
-        <v>0.437029105952359</v>
+        <v>0.9594835850649965</v>
       </c>
       <c r="E7" s="4">
-        <v>74.79050711193617</v>
+        <v>74.34446505875057</v>
       </c>
       <c r="F7" s="4">
-        <v>77.68812283912797</v>
+        <v>77.69956274150911</v>
       </c>
       <c r="G7" s="5">
         <v>44</v>
       </c>
       <c r="H7" s="5">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I7" s="5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J7" s="5">
         <v>3</v>
       </c>
       <c r="K7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-1.011616051095751</v>
+      </c>
+      <c r="O7" s="5">
+        <v>28</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.5437884112375829</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.4834545400597889</v>
+      </c>
+      <c r="R7" s="5">
+        <v>28</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
-        <v>0.8794218883250047</v>
+        <v>1.51110420011233</v>
       </c>
       <c r="C8" s="4">
-        <v>0.8794218883250047</v>
+        <v>1.340334657337853</v>
       </c>
       <c r="D8" s="4">
-        <v>0.8572633216817946</v>
+        <v>1.449183697505769</v>
       </c>
       <c r="E8" s="4">
-        <v>81.92677070828337</v>
+        <v>80.9303721488596</v>
       </c>
       <c r="F8" s="4">
-        <v>87.46348203711044</v>
+        <v>88.89590735623143</v>
       </c>
       <c r="G8" s="5">
         <v>17</v>
       </c>
       <c r="H8" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
@@ -1995,11 +2281,29 @@
         <v>0</v>
       </c>
       <c r="M8" s="5">
+        <v>2</v>
+      </c>
+      <c r="N8" s="4">
+        <v>-1.520951452411276</v>
+      </c>
+      <c r="O8" s="5">
+        <v>16</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.4186926801806889</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.434398267124351</v>
+      </c>
+      <c r="R8" s="5">
+        <v>16</v>
+      </c>
+      <c r="S8" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2010,6 +2314,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2017,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2028,9 +2333,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2064,8 +2375,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2087,66 +2406,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6131476005349534</v>
+        <v>0.3984178886811651</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5627765463554435</v>
+        <v>0.3944315241490254</v>
       </c>
       <c r="D3" s="4">
-        <v>0.597158669475116</v>
+        <v>0.3771380043926967</v>
       </c>
       <c r="E3" s="4">
-        <v>76.33786848072533</v>
+        <v>83.94132653061227</v>
       </c>
       <c r="F3" s="4">
-        <v>87.84279455630141</v>
+        <v>90.97152311707711</v>
       </c>
       <c r="G3" s="5">
         <v>48</v>
       </c>
       <c r="H3" s="5">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3692327602179196</v>
+      </c>
+      <c r="O3" s="5">
+        <v>47</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.168372575125227</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1673476456284487</v>
+      </c>
+      <c r="R3" s="5">
+        <v>47</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5291659954524742</v>
+        <v>0.2096603650921032</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4791204520962179</v>
+        <v>0.2042000745025837</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5107829181036964</v>
+        <v>0.2000033499711869</v>
       </c>
       <c r="E4" s="4">
-        <v>77.88681430018859</v>
+        <v>82.71602257924401</v>
       </c>
       <c r="F4" s="4">
-        <v>87.8830501213764</v>
+        <v>90.11780665429073</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
@@ -2169,34 +2524,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1712169317077298</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1227843390821378</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1230745647901931</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.27843776953119</v>
+        <v>0.3493300456753131</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2656623936193155</v>
+        <v>0.343478845019598</v>
       </c>
       <c r="D5" s="4">
-        <v>0.282012887050601</v>
+        <v>0.3388189982065262</v>
       </c>
       <c r="E5" s="4">
-        <v>78.29497756549443</v>
+        <v>83.35649153278308</v>
       </c>
       <c r="F5" s="4">
-        <v>88.53110571659755</v>
+        <v>89.19582083868708</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -2210,34 +2583,52 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2035589854777135</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2798859022968563</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.273926214262558</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
-        <v>0.5934832421805388</v>
+        <v>0.4606424419597763</v>
       </c>
       <c r="C6" s="4">
-        <v>0.5673705566853354</v>
+        <v>0.4368765975712264</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5453574135435216</v>
+        <v>0.419752419255657</v>
       </c>
       <c r="E6" s="4">
-        <v>78.89720332577522</v>
+        <v>83.16553287981938</v>
       </c>
       <c r="F6" s="4">
-        <v>88.38553318419144</v>
+        <v>91.05120556798495</v>
       </c>
       <c r="G6" s="5">
         <v>45</v>
       </c>
       <c r="H6" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5">
         <v>1</v>
@@ -2251,66 +2642,102 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.4363552352666134</v>
+      </c>
+      <c r="O6" s="5">
+        <v>44</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1437028436994595</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1226509910610527</v>
+      </c>
+      <c r="R6" s="5">
+        <v>44</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
-        <v>0.6576651215409458</v>
+        <v>0.3285976065704065</v>
       </c>
       <c r="C7" s="4">
-        <v>0.4922069213887579</v>
+        <v>0.2596640541314936</v>
       </c>
       <c r="D7" s="4">
-        <v>0.5546822807861769</v>
+        <v>0.2417247412907506</v>
       </c>
       <c r="E7" s="4">
-        <v>72.43661100803993</v>
+        <v>77.52705627705642</v>
       </c>
       <c r="F7" s="4">
-        <v>82.05384380720028</v>
+        <v>83.38799064470213</v>
       </c>
       <c r="G7" s="5">
         <v>44</v>
       </c>
       <c r="H7" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="5">
         <v>7</v>
       </c>
       <c r="J7" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.2256053229283404</v>
+      </c>
+      <c r="O7" s="5">
+        <v>35</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1915481536903302</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1351288845868397</v>
+      </c>
+      <c r="R7" s="5">
+        <v>35</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
-        <v>0.8109596567450559</v>
+        <v>0.4152222895613265</v>
       </c>
       <c r="C8" s="4">
-        <v>0.8109596567450559</v>
+        <v>0.4152222895613265</v>
       </c>
       <c r="D8" s="4">
-        <v>0.8180317127861002</v>
+        <v>0.4022171835595413</v>
       </c>
       <c r="E8" s="4">
-        <v>78.9435774309724</v>
+        <v>82.83913565426171</v>
       </c>
       <c r="F8" s="4">
-        <v>89.54533491248847</v>
+        <v>91.67390446111332</v>
       </c>
       <c r="G8" s="5">
         <v>17</v>
@@ -2333,9 +2760,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.3915042453071584</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2178631777897511</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2178631777897511</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2346,6 +2791,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2353,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2364,9 +2810,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2400,8 +2852,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2423,204 +2883,294 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6517036349012432</v>
+        <v>0.6102541603175256</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6517036349012432</v>
+        <v>0.5983137379949834</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6354416499966361</v>
+        <v>0.5951757647124383</v>
       </c>
       <c r="E3" s="4">
-        <v>83.89880952380956</v>
+        <v>81.26488095238089</v>
       </c>
       <c r="F3" s="4">
-        <v>91.72818791946305</v>
+        <v>88.31375838926169</v>
       </c>
       <c r="G3" s="5">
         <v>48</v>
       </c>
       <c r="H3" s="5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5983137379949834</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1835770875046185</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1872399983804469</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.431328922216427</v>
+        <v>0.5117008986349001</v>
       </c>
       <c r="C4" s="4">
-        <v>0.431328922216427</v>
+        <v>0.511893763266775</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4234572335359811</v>
+        <v>0.4751974720627903</v>
       </c>
       <c r="E4" s="4">
-        <v>85.10855405992194</v>
+        <v>81.4640324214791</v>
       </c>
       <c r="F4" s="4">
-        <v>92.04983578466364</v>
+        <v>86.6792803084391</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.511893763266775</v>
+      </c>
+      <c r="O4" s="5">
+        <v>41</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2070691214684806</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.194850209685867</v>
+      </c>
+      <c r="R4" s="5">
+        <v>41</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.408701541167898</v>
+        <v>0.4519771537424285</v>
       </c>
       <c r="C5" s="4">
-        <v>0.408701541167898</v>
+        <v>0.4466788524325532</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4041260705073029</v>
+        <v>0.4615801671260098</v>
       </c>
       <c r="E5" s="4">
-        <v>84.76769431176737</v>
+        <v>83.76103632942589</v>
       </c>
       <c r="F5" s="4">
-        <v>92.07054119663022</v>
+        <v>89.89433100099853</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.4466788524325532</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1232410204504358</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1239556427066542</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
-        <v>0.8482681759065318</v>
+        <v>0.7814285974899192</v>
       </c>
       <c r="C6" s="4">
-        <v>0.8482681759065318</v>
+        <v>0.7790792270936027</v>
       </c>
       <c r="D6" s="4">
-        <v>0.817103784071001</v>
+        <v>0.7351825880871143</v>
       </c>
       <c r="E6" s="4">
-        <v>85.28571428571438</v>
+        <v>83.00226757369644</v>
       </c>
       <c r="F6" s="4">
-        <v>92.14019388516044</v>
+        <v>88.77106636838319</v>
       </c>
       <c r="G6" s="5">
         <v>45</v>
       </c>
       <c r="H6" s="5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.7790792270936027</v>
+      </c>
+      <c r="O6" s="5">
+        <v>44</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1768353872114973</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1784516081064348</v>
+      </c>
+      <c r="R6" s="5">
+        <v>44</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
-        <v>0.7955993998990588</v>
+        <v>0.6281664793997771</v>
       </c>
       <c r="C7" s="4">
-        <v>0.7301202512472678</v>
+        <v>0.5327197413329954</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7011996659221743</v>
+        <v>0.437029105952359</v>
       </c>
       <c r="E7" s="4">
-        <v>79.61966604823726</v>
+        <v>74.79050711193617</v>
       </c>
       <c r="F7" s="4">
-        <v>84.57443563148314</v>
+        <v>77.68812283912797</v>
       </c>
       <c r="G7" s="5">
         <v>44</v>
       </c>
       <c r="H7" s="5">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J7" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <v>3</v>
@@ -2628,25 +3178,43 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.5327197413329954</v>
+      </c>
+      <c r="O7" s="5">
+        <v>33</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2611631383101298</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1958139852921594</v>
+      </c>
+      <c r="R7" s="5">
+        <v>33</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
-        <v>1.090896895999278</v>
+        <v>0.8794218883250047</v>
       </c>
       <c r="C8" s="4">
-        <v>1.090896895999278</v>
+        <v>0.8794218883250047</v>
       </c>
       <c r="D8" s="4">
-        <v>1.06791988044788</v>
+        <v>0.8572633216817946</v>
       </c>
       <c r="E8" s="4">
-        <v>81.84873949579838</v>
+        <v>81.92677070828337</v>
       </c>
       <c r="F8" s="4">
-        <v>86.74101855507382</v>
+        <v>87.46348203711044</v>
       </c>
       <c r="G8" s="5">
         <v>17</v>
@@ -2669,9 +3237,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.8794218883250047</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2096831607283641</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2096831607283641</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2682,6 +3268,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2689,7 +3276,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2700,9 +3287,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2736,8 +3329,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2759,25 +3360,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2825191564358601</v>
+        <v>0.6131476005349534</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2136988719138183</v>
+        <v>0.5627765463554435</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3001323416950633</v>
+        <v>0.597158669475116</v>
       </c>
       <c r="E3" s="4">
-        <v>84.01360544217677</v>
+        <v>76.33786848072533</v>
       </c>
       <c r="F3" s="4">
-        <v>90.7892897091711</v>
+        <v>87.84279455630141</v>
       </c>
       <c r="G3" s="5">
         <v>48</v>
@@ -2800,34 +3419,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5455849983432167</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2608026348095768</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2279988563225978</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3740370391302967</v>
+        <v>0.27843776953119</v>
       </c>
       <c r="C4" s="4">
-        <v>0.315216646917039</v>
+        <v>0.2656623936193155</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4032898552406914</v>
+        <v>0.282012887050601</v>
       </c>
       <c r="E4" s="4">
-        <v>86.13113330438576</v>
+        <v>78.29497756549443</v>
       </c>
       <c r="F4" s="4">
-        <v>92.18763387119822</v>
+        <v>88.53110571659755</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -2841,25 +3478,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2631214024031314</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09078650613944753</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08503160827514399</v>
+      </c>
+      <c r="R4" s="5">
+        <v>43</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1102315877276147</v>
+        <v>0.5291659954524742</v>
       </c>
       <c r="C5" s="4">
-        <v>0.09961394981962898</v>
+        <v>0.4791204520962179</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1125370231010427</v>
+        <v>0.5107829181036964</v>
       </c>
       <c r="E5" s="4">
-        <v>86.02475032566235</v>
+        <v>77.88681430018859</v>
       </c>
       <c r="F5" s="4">
-        <v>92.20691132371829</v>
+        <v>87.8830501213764</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
@@ -2882,34 +3537,52 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.4607732051547211</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2302436333589973</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1912333747569168</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1123968860372761</v>
+        <v>0.5934832421805388</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1050533677145385</v>
+        <v>0.5673705566853354</v>
       </c>
       <c r="D6" s="4">
-        <v>0.105997223694328</v>
+        <v>0.5453574135435216</v>
       </c>
       <c r="E6" s="4">
-        <v>88.64852607709801</v>
+        <v>78.89720332577522</v>
       </c>
       <c r="F6" s="4">
-        <v>93.41511309967795</v>
+        <v>88.38553318419144</v>
       </c>
       <c r="G6" s="5">
         <v>45</v>
       </c>
       <c r="H6" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
         <v>1</v>
@@ -2923,34 +3596,52 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.5673705566853354</v>
+      </c>
+      <c r="O6" s="5">
+        <v>43</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.177926607961923</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1588750351395903</v>
+      </c>
+      <c r="R6" s="5">
+        <v>43</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
-        <v>0.194095918296145</v>
+        <v>0.6576651215409458</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1494408248318671</v>
+        <v>0.4922069213887579</v>
       </c>
       <c r="D7" s="4">
-        <v>0.1914080875554496</v>
+        <v>0.5546822807861769</v>
       </c>
       <c r="E7" s="4">
-        <v>82.99319727891175</v>
+        <v>72.43661100803993</v>
       </c>
       <c r="F7" s="4">
-        <v>88.16224323774441</v>
+        <v>82.05384380720028</v>
       </c>
       <c r="G7" s="5">
         <v>44</v>
       </c>
       <c r="H7" s="5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I7" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" s="5">
         <v>3</v>
@@ -2964,25 +3655,43 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.4922069213887579</v>
+      </c>
+      <c r="O7" s="5">
+        <v>34</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.3367183493836611</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2048067178903377</v>
+      </c>
+      <c r="R7" s="5">
+        <v>34</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1464032526518468</v>
+        <v>0.8109596567450559</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1464032526518468</v>
+        <v>0.8109596567450559</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1348946355883613</v>
+        <v>0.8180317127861002</v>
       </c>
       <c r="E8" s="4">
-        <v>89.3517406962785</v>
+        <v>78.9435774309724</v>
       </c>
       <c r="F8" s="4">
-        <v>94.17686537702329</v>
+        <v>89.54533491248847</v>
       </c>
       <c r="G8" s="5">
         <v>17</v>
@@ -3005,9 +3714,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.8109596567450559</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2345924312889635</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2345924312889635</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3018,6 +3745,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3025,7 +3753,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3036,9 +3764,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -3072,8 +3806,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3095,236 +3837,344 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6517036349012432</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6517036349012432</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6354416499966361</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.89880952380956</v>
+      </c>
+      <c r="F3" s="4">
+        <v>91.72818791946305</v>
+      </c>
+      <c r="G3" s="5">
+        <v>48</v>
+      </c>
+      <c r="H3" s="5">
+        <v>48</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.6426294066039179</v>
+      </c>
+      <c r="O3" s="5">
+        <v>48</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1897936963084764</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1897936963084764</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.408701541167898</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.408701541167898</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4041260705073029</v>
+      </c>
+      <c r="E4" s="4">
+        <v>84.76769431176737</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.07054119663022</v>
+      </c>
+      <c r="G4" s="5">
+        <v>47</v>
+      </c>
+      <c r="H4" s="5">
+        <v>47</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.408701541167898</v>
+      </c>
+      <c r="O4" s="5">
+        <v>47</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07369008460991988</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07369008460991988</v>
+      </c>
+      <c r="R4" s="5">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.431328922216427</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.431328922216427</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4234572335359811</v>
+      </c>
+      <c r="E5" s="4">
+        <v>85.10855405992194</v>
+      </c>
+      <c r="F5" s="4">
+        <v>92.04983578466364</v>
+      </c>
+      <c r="G5" s="5">
+        <v>47</v>
+      </c>
+      <c r="H5" s="5">
+        <v>47</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4212879954042471</v>
+      </c>
+      <c r="O5" s="5">
+        <v>47</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1617767061458946</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1617767061458946</v>
+      </c>
+      <c r="R5" s="5">
+        <v>47</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.8482681759065318</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.8482681759065318</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.817103784071001</v>
+      </c>
+      <c r="E6" s="4">
+        <v>85.28571428571438</v>
+      </c>
+      <c r="F6" s="4">
+        <v>92.14019388516044</v>
+      </c>
+      <c r="G6" s="5">
+        <v>45</v>
+      </c>
+      <c r="H6" s="5">
+        <v>45</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-0.8482681759065318</v>
+      </c>
+      <c r="O6" s="5">
+        <v>45</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1115159913680134</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1115159913680134</v>
+      </c>
+      <c r="R6" s="5">
+        <v>45</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.7955993998990588</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.7301202512472678</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.7011996659221743</v>
+      </c>
+      <c r="E7" s="4">
+        <v>79.61966604823726</v>
+      </c>
+      <c r="F7" s="4">
+        <v>84.57443563148314</v>
+      </c>
+      <c r="G7" s="5">
         <v>44</v>
       </c>
-      <c r="B3" s="4">
-        <v>0.7704240143003043</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7704240143003043</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7450422590674932</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.84081632653061</v>
-      </c>
-      <c r="F3" s="4">
-        <v>91.18120805369128</v>
-      </c>
-      <c r="G3" s="5">
-        <v>25</v>
-      </c>
-      <c r="H3" s="5">
-        <v>25</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.8129444706212432</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6914772214827927</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.853121208142619</v>
-      </c>
-      <c r="E4" s="4">
-        <v>79.18488824101112</v>
-      </c>
-      <c r="F4" s="4">
-        <v>88.43799936081909</v>
-      </c>
-      <c r="G4" s="5">
-        <v>28</v>
-      </c>
-      <c r="H4" s="5">
-        <v>26</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
+      <c r="H7" s="5">
+        <v>36</v>
+      </c>
+      <c r="I7" s="5">
+        <v>4</v>
+      </c>
+      <c r="J7" s="5">
+        <v>4</v>
+      </c>
+      <c r="K7" s="5">
         <v>1</v>
       </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3986708723591048</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3915601590983965</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3998940018042136</v>
-      </c>
-      <c r="E5" s="4">
-        <v>82.24137931034483</v>
-      </c>
-      <c r="F5" s="4">
-        <v>90.59052688420839</v>
-      </c>
-      <c r="G5" s="5">
-        <v>29</v>
-      </c>
-      <c r="H5" s="5">
-        <v>28</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.8444852458724517</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.8198779456508294</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.7946010910529266</v>
-      </c>
-      <c r="E6" s="4">
-        <v>80.01700680272087</v>
-      </c>
-      <c r="F6" s="4">
-        <v>88.96618482188879</v>
-      </c>
-      <c r="G6" s="5">
-        <v>26</v>
-      </c>
-      <c r="H6" s="5">
-        <v>25</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.8961949704743307</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.8709340100145074</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.85862343163376</v>
-      </c>
-      <c r="E7" s="4">
-        <v>80.80535439982435</v>
-      </c>
-      <c r="F7" s="4">
-        <v>88.67972865699679</v>
-      </c>
-      <c r="G7" s="5">
-        <v>31</v>
-      </c>
-      <c r="H7" s="5">
-        <v>29</v>
-      </c>
-      <c r="I7" s="5">
-        <v>2</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
       <c r="L7" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.7301202512472678</v>
+      </c>
+      <c r="O7" s="5">
+        <v>36</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.224463485879946</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1766286792128469</v>
+      </c>
+      <c r="R7" s="5">
+        <v>36</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
-        <v>1.149353726003044</v>
+        <v>1.090896895999278</v>
       </c>
       <c r="C8" s="4">
-        <v>1.149353726003044</v>
+        <v>1.090896895999278</v>
       </c>
       <c r="D8" s="4">
-        <v>1.113936209879879</v>
+        <v>1.06791988044788</v>
       </c>
       <c r="E8" s="4">
-        <v>80.73283858998143</v>
+        <v>81.84873949579838</v>
       </c>
       <c r="F8" s="4">
-        <v>90.56436851738864</v>
+        <v>86.74101855507382</v>
       </c>
       <c r="G8" s="5">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H8" s="5">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
@@ -3341,9 +4191,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-1.090896895999278</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1281314266969151</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1281314266969151</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3354,6 +4222,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3361,7 +4230,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3372,9 +4241,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -3408,8 +4283,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3431,25 +4314,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2618801699451932</v>
+        <v>0.2825191564358601</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2036525811720929</v>
+        <v>0.2136988719138183</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2858156350873241</v>
+        <v>0.3001323416950633</v>
       </c>
       <c r="E3" s="4">
-        <v>83.59268707482984</v>
+        <v>84.01360544217677</v>
       </c>
       <c r="F3" s="4">
-        <v>90.49496644295185</v>
+        <v>90.7892897091711</v>
       </c>
       <c r="G3" s="5">
         <v>48</v>
@@ -3472,25 +4373,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1167499724393646</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.256191552038311</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1955914827927978</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3554159333917173</v>
+        <v>0.1102315877276147</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2991084852761345</v>
+        <v>0.09961394981962898</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3860283848649503</v>
+        <v>0.1125370231010427</v>
       </c>
       <c r="E4" s="4">
-        <v>85.66435084672182</v>
+        <v>86.02475032566235</v>
       </c>
       <c r="F4" s="4">
-        <v>91.89276024560922</v>
+        <v>92.20691132371829</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
@@ -3513,25 +4432,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.08477092318125273</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06130016405633793</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05312612838766875</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1133594276987107</v>
+        <v>0.3740370391302967</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1046220187713224</v>
+        <v>0.315216646917039</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1140177698775424</v>
+        <v>0.4032898552406914</v>
       </c>
       <c r="E5" s="4">
-        <v>85.66652192792023</v>
+        <v>86.13113330438576</v>
       </c>
       <c r="F5" s="4">
-        <v>91.91703555619009</v>
+        <v>92.18763387119822</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
@@ -3554,25 +4491,43 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2515596770605022</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2781415732535196</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.229934649984607</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1226635251260495</v>
+        <v>0.1123968860372761</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1158818715066453</v>
+        <v>0.1050533677145385</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1115232398502067</v>
+        <v>0.105997223694328</v>
       </c>
       <c r="E6" s="4">
-        <v>88.21315192743815</v>
+        <v>88.64852607709801</v>
       </c>
       <c r="F6" s="4">
-        <v>93.01864280387878</v>
+        <v>93.41511309967795</v>
       </c>
       <c r="G6" s="5">
         <v>45</v>
@@ -3595,34 +4550,52 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.0007481451180062858</v>
+      </c>
+      <c r="O6" s="5">
+        <v>44</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1124800132726102</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1051553875033576</v>
+      </c>
+      <c r="R6" s="5">
+        <v>44</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1993430656700947</v>
+        <v>0.194095918296145</v>
       </c>
       <c r="C7" s="4">
-        <v>0.1592086757783447</v>
+        <v>0.1494408248318671</v>
       </c>
       <c r="D7" s="4">
-        <v>0.192356707539496</v>
+        <v>0.1914080875554496</v>
       </c>
       <c r="E7" s="4">
-        <v>81.81431663574548</v>
+        <v>82.99319727891175</v>
       </c>
       <c r="F7" s="4">
-        <v>86.66412446613947</v>
+        <v>88.16224323774441</v>
       </c>
       <c r="G7" s="5">
         <v>44</v>
       </c>
       <c r="H7" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="5">
         <v>3</v>
@@ -3636,25 +4609,43 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.05661330721903306</v>
+      </c>
+      <c r="O7" s="5">
+        <v>37</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1908948621613526</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1527675922435784</v>
+      </c>
+      <c r="R7" s="5">
+        <v>37</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1383414500893014</v>
+        <v>0.1464032526518468</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1383414500893014</v>
+        <v>0.1464032526518468</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1215964323574105</v>
+        <v>0.1348946355883613</v>
       </c>
       <c r="E8" s="4">
-        <v>88.40936374549818</v>
+        <v>89.3517406962785</v>
       </c>
       <c r="F8" s="4">
-        <v>93.93012238452428</v>
+        <v>94.17686537702329</v>
       </c>
       <c r="G8" s="5">
         <v>17</v>
@@ -3677,9 +4668,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>0.01720128310267179</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1514624535643973</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1514624535643973</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3690,12 +4699,1774 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7704240143003043</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7704240143003043</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7450422590674932</v>
+      </c>
+      <c r="E3" s="4">
+        <v>82.84081632653061</v>
+      </c>
+      <c r="F3" s="4">
+        <v>91.18120805369128</v>
+      </c>
+      <c r="G3" s="5">
+        <v>25</v>
+      </c>
+      <c r="H3" s="5">
+        <v>25</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.7704240143003043</v>
+      </c>
+      <c r="O3" s="5">
+        <v>25</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1497167167520886</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1497167167520886</v>
+      </c>
+      <c r="R3" s="5">
+        <v>25</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3986708723591048</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3915601590983965</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3998940018042136</v>
+      </c>
+      <c r="E4" s="4">
+        <v>82.24137931034483</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.59052688420839</v>
+      </c>
+      <c r="G4" s="5">
+        <v>29</v>
+      </c>
+      <c r="H4" s="5">
+        <v>28</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3915601590983965</v>
+      </c>
+      <c r="O4" s="5">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06414406261806441</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05907025469154748</v>
+      </c>
+      <c r="R4" s="5">
+        <v>28</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.8129444706212432</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6914772214827927</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.853121208142619</v>
+      </c>
+      <c r="E5" s="4">
+        <v>79.18488824101112</v>
+      </c>
+      <c r="F5" s="4">
+        <v>88.43799936081909</v>
+      </c>
+      <c r="G5" s="5">
+        <v>28</v>
+      </c>
+      <c r="H5" s="5">
+        <v>26</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.6808911740706763</v>
+      </c>
+      <c r="O5" s="5">
+        <v>26</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3093731205131436</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1782509957192718</v>
+      </c>
+      <c r="R5" s="5">
+        <v>26</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.8444852458724517</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.8198779456508294</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.7946010910529266</v>
+      </c>
+      <c r="E6" s="4">
+        <v>80.01700680272087</v>
+      </c>
+      <c r="F6" s="4">
+        <v>88.96618482188879</v>
+      </c>
+      <c r="G6" s="5">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-0.8198779456508294</v>
+      </c>
+      <c r="O6" s="5">
+        <v>25</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1031704368292961</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.08170566207198079</v>
+      </c>
+      <c r="R6" s="5">
+        <v>25</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.8961949704743307</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.8709340100145074</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.85862343163376</v>
+      </c>
+      <c r="E7" s="4">
+        <v>80.80535439982435</v>
+      </c>
+      <c r="F7" s="4">
+        <v>88.67972865699679</v>
+      </c>
+      <c r="G7" s="5">
+        <v>31</v>
+      </c>
+      <c r="H7" s="5">
+        <v>29</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>-0.8709340100145074</v>
+      </c>
+      <c r="O7" s="5">
+        <v>29</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1073834049118654</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.08778606131080365</v>
+      </c>
+      <c r="R7" s="5">
+        <v>29</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1.149353726003044</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.149353726003044</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1.113936209879879</v>
+      </c>
+      <c r="E8" s="4">
+        <v>80.73283858998143</v>
+      </c>
+      <c r="F8" s="4">
+        <v>90.56436851738864</v>
+      </c>
+      <c r="G8" s="5">
+        <v>11</v>
+      </c>
+      <c r="H8" s="5">
+        <v>11</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>-1.149353726003044</v>
+      </c>
+      <c r="O8" s="5">
+        <v>11</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1623477842727474</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1623477842727474</v>
+      </c>
+      <c r="R8" s="5">
+        <v>11</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2618801699451932</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2036525811720929</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2858156350873241</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.59268707482984</v>
+      </c>
+      <c r="F3" s="4">
+        <v>90.49496644295185</v>
+      </c>
+      <c r="G3" s="5">
+        <v>48</v>
+      </c>
+      <c r="H3" s="5">
+        <v>44</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1053346253210952</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2352070947668654</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.184130556006744</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1133594276987107</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1046220187713224</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1140177698775424</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.66652192792023</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.91703555619009</v>
+      </c>
+      <c r="G4" s="5">
+        <v>47</v>
+      </c>
+      <c r="H4" s="5">
+        <v>44</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.0851414202345725</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06268818238159043</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0563010126531194</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3554159333917173</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2991084852761345</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3860283848649503</v>
+      </c>
+      <c r="E5" s="4">
+        <v>85.66435084672182</v>
+      </c>
+      <c r="F5" s="4">
+        <v>91.89276024560922</v>
+      </c>
+      <c r="G5" s="5">
+        <v>47</v>
+      </c>
+      <c r="H5" s="5">
+        <v>44</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2318937471271696</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.268647180531155</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2222346183882954</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.1226635251260495</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.1158818715066453</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.1115232398502067</v>
+      </c>
+      <c r="E6" s="4">
+        <v>88.21315192743815</v>
+      </c>
+      <c r="F6" s="4">
+        <v>93.01864280387878</v>
+      </c>
+      <c r="G6" s="5">
+        <v>45</v>
+      </c>
+      <c r="H6" s="5">
+        <v>44</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-0.005721403602499888</v>
+      </c>
+      <c r="O6" s="5">
+        <v>44</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1232992366374384</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1166620629069862</v>
+      </c>
+      <c r="R6" s="5">
+        <v>44</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.1993430656700947</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.1592086757783447</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.192356707539496</v>
+      </c>
+      <c r="E7" s="4">
+        <v>81.81431663574548</v>
+      </c>
+      <c r="F7" s="4">
+        <v>86.66412446613947</v>
+      </c>
+      <c r="G7" s="5">
+        <v>44</v>
+      </c>
+      <c r="H7" s="5">
+        <v>36</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5</v>
+      </c>
+      <c r="J7" s="5">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>-0.04680349482202124</v>
+      </c>
+      <c r="O7" s="5">
+        <v>36</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1923021660846673</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1584037143109369</v>
+      </c>
+      <c r="R7" s="5">
+        <v>36</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.1383414500893014</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.1383414500893014</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.1215964323574105</v>
+      </c>
+      <c r="E8" s="4">
+        <v>88.40936374549818</v>
+      </c>
+      <c r="F8" s="4">
+        <v>93.93012238452428</v>
+      </c>
+      <c r="G8" s="5">
+        <v>17</v>
+      </c>
+      <c r="H8" s="5">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0.05286982362951065</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.154301687587788</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.154301687587788</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>95.16129032258065</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.629032258064516</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.209677419354839</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.4032258064516129</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1895609371654502</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1696003315636369</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1604266676659607</v>
+      </c>
+      <c r="K3" s="4">
+        <v>84.39927583936779</v>
+      </c>
+      <c r="L3" s="4">
+        <v>89.88972180125587</v>
+      </c>
+      <c r="M3" s="5">
+        <v>248</v>
+      </c>
+      <c r="N3" s="5">
+        <v>655574.7041702271</v>
+      </c>
+      <c r="O3" s="4">
+        <v>30.64722098874419</v>
+      </c>
+      <c r="P3" s="5">
+        <v>21391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>85.48387096774194</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.064516129032258</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6.451612903225806</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.4032258064516129</v>
+      </c>
+      <c r="F4" s="3">
+        <v>6.048387096774194</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.2394210816311978</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2093883928615733</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2196177412357103</v>
+      </c>
+      <c r="K4" s="4">
+        <v>76.98472130787789</v>
+      </c>
+      <c r="L4" s="4">
+        <v>85.14379014216604</v>
+      </c>
+      <c r="M4" s="5">
+        <v>248</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1093849.855422974</v>
+      </c>
+      <c r="O4" s="4">
+        <v>38.78487591472445</v>
+      </c>
+      <c r="P4" s="5">
+        <v>28203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>91.12903225806451</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.82258064516129</v>
+      </c>
+      <c r="D5" s="3">
+        <v>6.048387096774194</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>6.048387096774194</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1435095455299537</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1246347213674834</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1493833212724185</v>
+      </c>
+      <c r="K5" s="4">
+        <v>79.10508558261978</v>
+      </c>
+      <c r="L5" s="4">
+        <v>87.49170094537011</v>
+      </c>
+      <c r="M5" s="5">
+        <v>248</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2966560.71138382</v>
+      </c>
+      <c r="O5" s="4">
+        <v>125.8190139699644</v>
+      </c>
+      <c r="P5" s="5">
+        <v>23578</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>84.2741935483871</v>
+      </c>
+      <c r="C6" s="3">
+        <v>10.08064516129032</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2169189215879219</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.187727891479589</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2125789493694034</v>
+      </c>
+      <c r="K6" s="4">
+        <v>79.31232170287464</v>
+      </c>
+      <c r="L6" s="4">
+        <v>85.27526701306174</v>
+      </c>
+      <c r="M6" s="5">
+        <v>248</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1861526.801586151</v>
+      </c>
+      <c r="O6" s="4">
+        <v>80.79894099510183</v>
+      </c>
+      <c r="P6" s="5">
+        <v>23039</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>95.96774193548387</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.419354838709677</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.612903225806452</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1.612903225806452</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1235811747808591</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1031114927381785</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.09576834730424615</v>
+      </c>
+      <c r="K7" s="4">
+        <v>83.78154487601485</v>
+      </c>
+      <c r="L7" s="4">
+        <v>91.05474669841858</v>
+      </c>
+      <c r="M7" s="5">
+        <v>248</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2370727.339029312</v>
+      </c>
+      <c r="O7" s="4">
+        <v>137.1869300983341</v>
+      </c>
+      <c r="P7" s="5">
+        <v>17281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>89.51612903225806</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4.032258064516129</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6.451612903225806</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1835616936098166</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1363952672925121</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1649637887907667</v>
+      </c>
+      <c r="K8" s="4">
+        <v>81.38742593811746</v>
+      </c>
+      <c r="L8" s="4">
+        <v>88.7541946308726</v>
+      </c>
+      <c r="M8" s="5">
+        <v>248</v>
+      </c>
+      <c r="N8" s="5">
+        <v>231237.4997138977</v>
+      </c>
+      <c r="O8" s="4">
+        <v>10.10035379199344</v>
+      </c>
+      <c r="P8" s="5">
+        <v>22894</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>83.06451612903226</v>
+      </c>
+      <c r="C9" s="3">
+        <v>10.48387096774194</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6.451612903225806</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.209677419354839</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5.241935483870968</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3600110351073317</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3383483889884761</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3212847509719741</v>
+      </c>
+      <c r="K9" s="4">
+        <v>80.38073293833662</v>
+      </c>
+      <c r="L9" s="4">
+        <v>85.95290286497755</v>
+      </c>
+      <c r="M9" s="5">
+        <v>248</v>
+      </c>
+      <c r="N9" s="5">
+        <v>732794.2359447479</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.03558940794047</v>
+      </c>
+      <c r="P9" s="5">
+        <v>26138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>93.14516129032258</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.82258064516129</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4.032258064516129</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4.032258064516129</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1838943778310467</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.169537671915626</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1711625961352542</v>
+      </c>
+      <c r="K10" s="4">
+        <v>82.24393789774015</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.19034603449499</v>
+      </c>
+      <c r="M10" s="5">
+        <v>248</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1647885.342121124</v>
+      </c>
+      <c r="O10" s="4">
+        <v>87.84505262120177</v>
+      </c>
+      <c r="P10" s="5">
+        <v>18759</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>89.91935483870968</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4.435483870967742</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1909260528748227</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1773982637159622</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1803309130267485</v>
+      </c>
+      <c r="K11" s="4">
+        <v>80.98762892253613</v>
+      </c>
+      <c r="L11" s="4">
+        <v>86.44304322725034</v>
+      </c>
+      <c r="M11" s="5">
+        <v>248</v>
+      </c>
+      <c r="N11" s="5">
+        <v>835513.822555542</v>
+      </c>
+      <c r="O11" s="4">
+        <v>38.90815975391367</v>
+      </c>
+      <c r="P11" s="5">
+        <v>21474</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>90.7258064516129</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.629032258064516</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2194246737514782</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1772697936645159</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1789539969459544</v>
+      </c>
+      <c r="K12" s="4">
+        <v>76.95317643186264</v>
+      </c>
+      <c r="L12" s="4">
+        <v>87.16898498953437</v>
+      </c>
+      <c r="M12" s="5">
+        <v>248</v>
+      </c>
+      <c r="N12" s="5">
+        <v>361978.0004024506</v>
+      </c>
+      <c r="O12" s="4">
+        <v>17.91438188668963</v>
+      </c>
+      <c r="P12" s="5">
+        <v>20206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>96.7741935483871</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1.612903225806452</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.612903225806452</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.4032258064516129</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.209677419354839</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1502011444857094</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1405505121058367</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1229462899835287</v>
+      </c>
+      <c r="K13" s="4">
+        <v>83.64466754443676</v>
+      </c>
+      <c r="L13" s="4">
+        <v>90.31770946092313</v>
+      </c>
+      <c r="M13" s="5">
+        <v>248</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1404903.701543808</v>
+      </c>
+      <c r="O13" s="4">
+        <v>70.38595699117275</v>
+      </c>
+      <c r="P13" s="5">
+        <v>19960</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>92.74193548387096</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.612903225806452</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1785757757837256</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1474556485435571</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1828444353933343</v>
+      </c>
+      <c r="K14" s="4">
+        <v>85.82194974764056</v>
+      </c>
+      <c r="L14" s="4">
+        <v>91.56554449014902</v>
+      </c>
+      <c r="M14" s="5">
+        <v>248</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2700647.239685059</v>
+      </c>
+      <c r="O14" s="4">
+        <v>200.4190901436036</v>
+      </c>
+      <c r="P14" s="5">
+        <v>13475</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>96</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1470845709728257</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1139282909422198</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1423539921885571</v>
+      </c>
+      <c r="K15" s="4">
+        <v>80.97777777777814</v>
+      </c>
+      <c r="L15" s="4">
+        <v>89.60879940343271</v>
+      </c>
+      <c r="M15" s="5">
+        <v>150</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2567930.019378662</v>
+      </c>
+      <c r="O15" s="4">
+        <v>211.9103828501949</v>
+      </c>
+      <c r="P15" s="5">
+        <v>12118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>92.33870967741935</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2.016129032258065</v>
+      </c>
+      <c r="D16" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>5.64516129032258</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1753854526254478</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1476685825424127</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1785527342531132</v>
+      </c>
+      <c r="K16" s="4">
+        <v>85.23137480798727</v>
+      </c>
+      <c r="L16" s="4">
+        <v>91.04310998051483</v>
+      </c>
+      <c r="M16" s="5">
+        <v>248</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1299178.620815277</v>
+      </c>
+      <c r="O16" s="4">
+        <v>94.08883406831382</v>
+      </c>
+      <c r="P16" s="5">
+        <v>13808</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3809,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>1</v>
@@ -3853,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
         <v>13</v>
@@ -4029,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
         <v>4</v>
@@ -4073,16 +6844,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -4337,7 +7108,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
         <v>1</v>
@@ -4406,9 +7177,720 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>236</v>
+      </c>
+      <c r="C3" s="5">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>212</v>
+      </c>
+      <c r="C4" s="5">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>226</v>
+      </c>
+      <c r="C5" s="5">
+        <v>7</v>
+      </c>
+      <c r="D5" s="5">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>12</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>209</v>
+      </c>
+      <c r="C6" s="5">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5">
+        <v>14</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>13</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>238</v>
+      </c>
+      <c r="C7" s="5">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>4</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>222</v>
+      </c>
+      <c r="C8" s="5">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5">
+        <v>14</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>206</v>
+      </c>
+      <c r="C9" s="5">
+        <v>26</v>
+      </c>
+      <c r="D9" s="5">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5">
+        <v>13</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5">
+        <v>3</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>8</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>231</v>
+      </c>
+      <c r="C10" s="5">
+        <v>7</v>
+      </c>
+      <c r="D10" s="5">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>10</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>223</v>
+      </c>
+      <c r="C11" s="5">
+        <v>11</v>
+      </c>
+      <c r="D11" s="5">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>14</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>7</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>225</v>
+      </c>
+      <c r="C12" s="5">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5">
+        <v>14</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>14</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>12</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>240</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>230</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5">
+        <v>14</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>14</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>14</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>144</v>
+      </c>
+      <c r="C15" s="5">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>229</v>
+      </c>
+      <c r="C16" s="5">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5">
+        <v>14</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>14</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>14</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4419,9 +7901,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -4455,8 +7943,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4478,10 +7974,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>0.6140422242410435</v>
@@ -4519,40 +8033,58 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6140422242410435</v>
+      </c>
+      <c r="O3" s="5">
+        <v>48</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.186571702807763</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.186571702807763</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4815977326415096</v>
+        <v>0.3537336632492693</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4188075956833129</v>
+        <v>0.3537336632492693</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3952710500334295</v>
+        <v>0.3503599287547963</v>
       </c>
       <c r="E4" s="4">
-        <v>85.6107975104936</v>
+        <v>86.46258503401371</v>
       </c>
       <c r="F4" s="4">
-        <v>90.9186539102304</v>
+        <v>92.65029273168649</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -4560,40 +8092,58 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.353702341848505</v>
+      </c>
+      <c r="O4" s="5">
+        <v>47</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09262593081684253</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09262593081684253</v>
+      </c>
+      <c r="R4" s="5">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3537336632492693</v>
+        <v>0.4815977326415096</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3537336632492693</v>
+        <v>0.4188075956833129</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3503599287547963</v>
+        <v>0.3952710500334295</v>
       </c>
       <c r="E5" s="4">
-        <v>86.46258503401371</v>
+        <v>85.6107975104936</v>
       </c>
       <c r="F5" s="4">
-        <v>92.65029273168649</v>
+        <v>90.9186539102304</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -4601,10 +8151,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.357150895494674</v>
+      </c>
+      <c r="O5" s="5">
+        <v>45</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2596674898443894</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2028871596727505</v>
+      </c>
+      <c r="R5" s="5">
+        <v>45</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
         <v>0.8128093356423173</v>
@@ -4642,10 +8210,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.790418022701906</v>
+      </c>
+      <c r="O6" s="5">
+        <v>42</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.09292464255091952</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.07557142458268748</v>
+      </c>
+      <c r="R6" s="5">
+        <v>42</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
         <v>0.9448312672557925</v>
@@ -4683,10 +8269,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.9077506373194685</v>
+      </c>
+      <c r="O7" s="5">
+        <v>38</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.3017812221443546</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.2879451149167166</v>
+      </c>
+      <c r="R7" s="5">
+        <v>38</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
         <v>1.451280154145676</v>
@@ -4724,9 +8328,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-1.417932163512386</v>
+      </c>
+      <c r="O8" s="5">
+        <v>16</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2375233660022435</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2169363363295126</v>
+      </c>
+      <c r="R8" s="5">
+        <v>16</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4737,14 +8359,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4755,9 +8378,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -4791,8 +8420,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4814,10 +8451,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>0.7069956452085552</v>
@@ -4855,92 +8510,146 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6645774570335132</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2205662895333053</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2052891990047164</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5492060180990397</v>
+        <v>0.391656337492283</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4548682704940959</v>
+        <v>0.3735797496244788</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4832469781573906</v>
+        <v>0.356277130611673</v>
       </c>
       <c r="E4" s="4">
-        <v>78.95570994355212</v>
+        <v>77.56911275148381</v>
       </c>
       <c r="F4" s="4">
-        <v>87.27069351230567</v>
+        <v>84.21486029796661</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3735797496244788</v>
+      </c>
+      <c r="O4" s="5">
+        <v>41</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1187520810694531</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1032273149071149</v>
+      </c>
+      <c r="R4" s="5">
+        <v>41</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.391656337492283</v>
+        <v>0.5492060180990397</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3735797496244788</v>
+        <v>0.4548682704940959</v>
       </c>
       <c r="D5" s="4">
-        <v>0.356277130611673</v>
+        <v>0.4832469781573906</v>
       </c>
       <c r="E5" s="4">
-        <v>77.56911275148381</v>
+        <v>78.95570994355212</v>
       </c>
       <c r="F5" s="4">
-        <v>84.21486029796661</v>
+        <v>87.27069351230567</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.405890097951953</v>
+      </c>
+      <c r="O5" s="5">
+        <v>42</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2966187280030061</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2205313146666242</v>
+      </c>
+      <c r="R5" s="5">
+        <v>42</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
         <v>0.9771286283465815</v>
@@ -4978,10 +8687,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.9868391320546586</v>
+      </c>
+      <c r="O6" s="5">
+        <v>36</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1385409266204578</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1240523874165411</v>
+      </c>
+      <c r="R6" s="5">
+        <v>36</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
         <v>1.087020076390536</v>
@@ -5019,10 +8746,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-1.035463315295117</v>
+      </c>
+      <c r="O7" s="5">
+        <v>32</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.3908026243674586</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.3612478845567676</v>
+      </c>
+      <c r="R7" s="5">
+        <v>32</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
         <v>1.330174567364455</v>
@@ -5060,9 +8805,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-1.330174567364455</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.343362420614356</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.343362420614356</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5073,14 +8836,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5091,9 +8855,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -5127,8 +8897,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5150,10 +8928,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>0.4797917103422138</v>
@@ -5191,92 +8987,146 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4678319861899814</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1164768322184685</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1119173840225058</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3339702120489118</v>
+        <v>0.2266415133705176</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3150183054419985</v>
+        <v>0.2411210256368412</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3609609182485861</v>
+        <v>0.2378474501181995</v>
       </c>
       <c r="E4" s="4">
-        <v>81.39021566073208</v>
+        <v>80.14184397163149</v>
       </c>
       <c r="F4" s="4">
-        <v>89.48974249131376</v>
+        <v>88.28359274596585</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.213804037818985</v>
+      </c>
+      <c r="O4" s="5">
+        <v>43</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.125381375437093</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1223038081658134</v>
+      </c>
+      <c r="R4" s="5">
+        <v>43</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2266415133705176</v>
+        <v>0.3339702120489118</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2411210256368412</v>
+        <v>0.3150183054419985</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2378474501181995</v>
+        <v>0.3609609182485861</v>
       </c>
       <c r="E5" s="4">
-        <v>80.14184397163149</v>
+        <v>81.39021566073208</v>
       </c>
       <c r="F5" s="4">
-        <v>88.28359274596585</v>
+        <v>89.48974249131376</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3144529938769545</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1357253369446107</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1236806217397431</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
         <v>0.5752870883355686</v>
@@ -5314,10 +9164,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.5794800660268105</v>
+      </c>
+      <c r="O6" s="5">
+        <v>44</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1478120137870358</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.146288438909806</v>
+      </c>
+      <c r="R6" s="5">
+        <v>44</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
         <v>0.5090861351847417</v>
@@ -5355,10 +9223,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.4124154327093378</v>
+      </c>
+      <c r="O7" s="5">
+        <v>34</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2081037845801373</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1231183232732804</v>
+      </c>
+      <c r="R7" s="5">
+        <v>34</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
         <v>0.718572604163465</v>
@@ -5396,9 +9282,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.718572604163465</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1129033365329009</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1129033365329009</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5409,14 +9313,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5427,9 +9332,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -5463,8 +9374,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5486,10 +9405,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>0.5085220553008173</v>
@@ -5527,34 +9464,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5341659621715636</v>
+      </c>
+      <c r="O3" s="5">
+        <v>44</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2174215070762396</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2092119274969017</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4203505965650871</v>
+        <v>0.325887852118644</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3925563693650262</v>
+        <v>0.3267770779900731</v>
       </c>
       <c r="D4" s="4">
-        <v>0.389923768896721</v>
+        <v>0.3022347733261737</v>
       </c>
       <c r="E4" s="4">
-        <v>82.14502822405565</v>
+        <v>81.19626574033917</v>
       </c>
       <c r="F4" s="4">
-        <v>89.11680708267806</v>
+        <v>87.80665429101762</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -5568,34 +9523,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3267770779900731</v>
+      </c>
+      <c r="O4" s="5">
+        <v>41</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1492304208900516</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1288614452528272</v>
+      </c>
+      <c r="R4" s="5">
+        <v>41</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.325887852118644</v>
+        <v>0.4203505965650871</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3267770779900731</v>
+        <v>0.3925563693650262</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3022347733261737</v>
+        <v>0.389923768896721</v>
       </c>
       <c r="E5" s="4">
-        <v>81.19626574033917</v>
+        <v>82.14502822405565</v>
       </c>
       <c r="F5" s="4">
-        <v>87.80665429101762</v>
+        <v>89.11680708267806</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -5609,10 +9582,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3464060029750735</v>
+      </c>
+      <c r="O5" s="5">
+        <v>43</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2973927041664368</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2638803033504866</v>
+      </c>
+      <c r="R5" s="5">
+        <v>43</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
         <v>0.7284589404396805</v>
@@ -5650,10 +9641,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.7227549507689637</v>
+      </c>
+      <c r="O6" s="5">
+        <v>43</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1515524298397479</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1394996156431991</v>
+      </c>
+      <c r="R6" s="5">
+        <v>43</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
         <v>0.6816437457189621</v>
@@ -5691,10 +9700,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.5788046151167442</v>
+      </c>
+      <c r="O7" s="5">
+        <v>21</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2741631665357187</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1864673367212445</v>
+      </c>
+      <c r="R7" s="5">
+        <v>21</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
         <v>0.7300725354322973</v>
@@ -5732,9 +9759,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.7300725354322973</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.2050196862429353</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.2050196862429353</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5745,14 +9790,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5763,9 +9809,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -5799,8 +9851,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5822,10 +9882,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4">
         <v>0.475405493421751</v>
@@ -5863,34 +9941,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4578881692913476</v>
+      </c>
+      <c r="O3" s="5">
+        <v>47</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1323256648779523</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1219831803200562</v>
+      </c>
+      <c r="R3" s="5">
+        <v>47</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4196131955669195</v>
+        <v>0.2348727465667823</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4196131955669195</v>
+        <v>0.2313059660606379</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4138656236623109</v>
+        <v>0.2331422436468344</v>
       </c>
       <c r="E4" s="4">
-        <v>85.18454190186714</v>
+        <v>84.61137646547972</v>
       </c>
       <c r="F4" s="4">
-        <v>92.18477795230611</v>
+        <v>92.18192203341401</v>
       </c>
       <c r="G4" s="5">
         <v>47</v>
       </c>
       <c r="H4" s="5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -5904,34 +10000,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2313059660606379</v>
+      </c>
+      <c r="O4" s="5">
+        <v>46</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06610334457985753</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06389605459705469</v>
+      </c>
+      <c r="R4" s="5">
+        <v>46</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2348727465667823</v>
+        <v>0.4196131955669195</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2313059660606379</v>
+        <v>0.4196131955669195</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2331422436468344</v>
+        <v>0.4138656236623109</v>
       </c>
       <c r="E5" s="4">
-        <v>84.61137646547972</v>
+        <v>85.18454190186714</v>
       </c>
       <c r="F5" s="4">
-        <v>92.18192203341401</v>
+        <v>92.18477795230611</v>
       </c>
       <c r="G5" s="5">
         <v>47</v>
       </c>
       <c r="H5" s="5">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -5945,10 +10059,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.4075123728131878</v>
+      </c>
+      <c r="O5" s="5">
+        <v>47</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1358370206036792</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1358370206036792</v>
+      </c>
+      <c r="R5" s="5">
+        <v>47</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
         <v>0.4313400541278315</v>
@@ -5986,10 +10118,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.4191140409711466</v>
+      </c>
+      <c r="O6" s="5">
+        <v>44</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.08500029579667751</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.0744282436090833</v>
+      </c>
+      <c r="R6" s="5">
+        <v>44</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4">
         <v>0.4713144128829008</v>
@@ -6027,10 +10177,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.362874313814085</v>
+      </c>
+      <c r="O7" s="5">
+        <v>37</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.2005976984855523</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1095928209280108</v>
+      </c>
+      <c r="R7" s="5">
+        <v>37</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4">
         <v>0.5447004633246457</v>
@@ -6068,9 +10236,27 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
+      <c r="N8" s="4">
+        <v>-0.5447004633246457</v>
+      </c>
+      <c r="O8" s="5">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1267053072747257</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1267053072747257</v>
+      </c>
+      <c r="R8" s="5">
+        <v>17</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -6081,678 +10267,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5520864058356206</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4769349366648613</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5341009102404671</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.35841836734662</v>
-      </c>
-      <c r="F3" s="4">
-        <v>89.43372483221356</v>
-      </c>
-      <c r="G3" s="5">
-        <v>48</v>
-      </c>
-      <c r="H3" s="5">
-        <v>44</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3946334729471804</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2995955871370625</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3630551188633059</v>
-      </c>
-      <c r="E4" s="4">
-        <v>82.83687943262461</v>
-      </c>
-      <c r="F4" s="4">
-        <v>90.33604645628159</v>
-      </c>
-      <c r="G4" s="5">
-        <v>47</v>
-      </c>
-      <c r="H4" s="5">
-        <v>43</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2601331070877048</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2436140013744392</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2572585760861571</v>
-      </c>
-      <c r="E5" s="4">
-        <v>82.32739904472481</v>
-      </c>
-      <c r="F5" s="4">
-        <v>90.12780237041231</v>
-      </c>
-      <c r="G5" s="5">
-        <v>47</v>
-      </c>
-      <c r="H5" s="5">
-        <v>43</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.6483844529519606</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.6159858620658536</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.5865848125711979</v>
-      </c>
-      <c r="E6" s="4">
-        <v>82.96674225245683</v>
-      </c>
-      <c r="F6" s="4">
-        <v>90.1807109122537</v>
-      </c>
-      <c r="G6" s="5">
-        <v>45</v>
-      </c>
-      <c r="H6" s="5">
-        <v>42</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>2</v>
-      </c>
-      <c r="K6" s="5">
-        <v>1</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.4877421573100326</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.4031812497024094</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.4035089983676503</v>
-      </c>
-      <c r="E7" s="4">
-        <v>76.81354359925814</v>
-      </c>
-      <c r="F7" s="4">
-        <v>82.79896278218374</v>
-      </c>
-      <c r="G7" s="5">
-        <v>44</v>
-      </c>
-      <c r="H7" s="5">
-        <v>34</v>
-      </c>
-      <c r="I7" s="5">
-        <v>7</v>
-      </c>
-      <c r="J7" s="5">
-        <v>3</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>3</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.5855863066526477</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.5634675455134803</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.5805263087183876</v>
-      </c>
-      <c r="E8" s="4">
-        <v>82.52100840336145</v>
-      </c>
-      <c r="F8" s="4">
-        <v>90.30201342281914</v>
-      </c>
-      <c r="G8" s="5">
-        <v>17</v>
-      </c>
-      <c r="H8" s="5">
-        <v>16</v>
-      </c>
-      <c r="I8" s="5">
-        <v>1</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.854716163628047</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7852927012475067</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.8130253372120313</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.15858843537451</v>
-      </c>
-      <c r="F3" s="4">
-        <v>89.27875652498163</v>
-      </c>
-      <c r="G3" s="5">
-        <v>48</v>
-      </c>
-      <c r="H3" s="5">
-        <v>42</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>6</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4570295425017177</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3531214953840928</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3479338418626124</v>
-      </c>
-      <c r="E4" s="4">
-        <v>82.70589086698503</v>
-      </c>
-      <c r="F4" s="4">
-        <v>87.19191774953553</v>
-      </c>
-      <c r="G4" s="5">
-        <v>47</v>
-      </c>
-      <c r="H4" s="5">
-        <v>39</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.389984977227257</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3707292246939776</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3233822575292674</v>
-      </c>
-      <c r="E5" s="4">
-        <v>82.18772615429133</v>
-      </c>
-      <c r="F5" s="4">
-        <v>87.40325574753797</v>
-      </c>
-      <c r="G5" s="5">
-        <v>47</v>
-      </c>
-      <c r="H5" s="5">
-        <v>40</v>
-      </c>
-      <c r="I5" s="5">
-        <v>3</v>
-      </c>
-      <c r="J5" s="5">
-        <v>4</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.165649017479611</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1.065595186329314</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1.064581453257063</v>
-      </c>
-      <c r="E6" s="4">
-        <v>80.92970521541973</v>
-      </c>
-      <c r="F6" s="4">
-        <v>86.55456127268302</v>
-      </c>
-      <c r="G6" s="5">
-        <v>45</v>
-      </c>
-      <c r="H6" s="5">
-        <v>36</v>
-      </c>
-      <c r="I6" s="5">
-        <v>5</v>
-      </c>
-      <c r="J6" s="5">
-        <v>4</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1.179442865772284</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1.024270833361865</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.9594835850649965</v>
-      </c>
-      <c r="E7" s="4">
-        <v>74.34446505875057</v>
-      </c>
-      <c r="F7" s="4">
-        <v>77.69956274150911</v>
-      </c>
-      <c r="G7" s="5">
-        <v>44</v>
-      </c>
-      <c r="H7" s="5">
-        <v>28</v>
-      </c>
-      <c r="I7" s="5">
-        <v>13</v>
-      </c>
-      <c r="J7" s="5">
-        <v>3</v>
-      </c>
-      <c r="K7" s="5">
-        <v>1</v>
-      </c>
-      <c r="L7" s="5">
-        <v>2</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1.51110420011233</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1.340334657337853</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1.449183697505769</v>
-      </c>
-      <c r="E8" s="4">
-        <v>80.9303721488596</v>
-      </c>
-      <c r="F8" s="4">
-        <v>88.89590735623143</v>
-      </c>
-      <c r="G8" s="5">
-        <v>17</v>
-      </c>
-      <c r="H8" s="5">
-        <v>14</v>
-      </c>
-      <c r="I8" s="5">
-        <v>1</v>
-      </c>
-      <c r="J8" s="5">
-        <v>2</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/MontoyaThe2015.xlsx
+++ b/public/downloads/MontoyaThe2015.xlsx
@@ -1512,16 +1512,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4758329141124376</v>
+        <v>-0.4702551583774019</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.194315164748972</v>
+        <v>0.194556019360894</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1298965749441935</v>
+        <v>0.1296522567267414</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -1571,16 +1571,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.243394020424158</v>
+        <v>-0.277285545540786</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08567385012778073</v>
+        <v>0.07813648648574056</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07556728055072301</v>
+        <v>0.07048146681329565</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -1630,16 +1630,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2554322134533396</v>
+        <v>-0.2925139985359615</v>
       </c>
       <c r="O5" s="5">
         <v>43</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2344497486249714</v>
+        <v>0.230504877871501</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1482721873851913</v>
+        <v>0.1474098202902466</v>
       </c>
       <c r="R5" s="5">
         <v>43</v>
@@ -1689,16 +1689,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6159858620658536</v>
+        <v>-0.5488188418047588</v>
       </c>
       <c r="O6" s="5">
         <v>42</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1683761362303682</v>
+        <v>0.1644452356368464</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1456902271545656</v>
+        <v>0.1366809036428569</v>
       </c>
       <c r="R6" s="5">
         <v>42</v>
@@ -1748,16 +1748,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4031812497024094</v>
+        <v>-0.3906553812480763</v>
       </c>
       <c r="O7" s="5">
         <v>34</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2274745341778402</v>
+        <v>0.2280522476728508</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1656374996267651</v>
+        <v>0.1649114972727397</v>
       </c>
       <c r="R7" s="5">
         <v>34</v>
@@ -1807,13 +1807,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.5634675455134803</v>
+        <v>-0.5354403136921085</v>
       </c>
       <c r="O8" s="5">
         <v>16</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2096798430419383</v>
+        <v>0.2113285037373131</v>
       </c>
       <c r="Q8" s="4">
         <v>0.1992836495216942</v>
@@ -1989,13 +1989,13 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8450265093239963</v>
+        <v>-0.846945388501371</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3608030018556369</v>
+        <v>0.3606430952575223</v>
       </c>
       <c r="Q3" s="4">
         <v>0.3830327427835485</v>
@@ -2048,16 +2048,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3570389620968748</v>
+        <v>-0.3508540858174102</v>
       </c>
       <c r="O4" s="5">
         <v>40</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1750622924696615</v>
+        <v>0.1757202638210087</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1806768884707559</v>
+        <v>0.1803676514596826</v>
       </c>
       <c r="R4" s="5">
         <v>40</v>
@@ -2107,16 +2107,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2543870006858363</v>
+        <v>-0.188198061233086</v>
       </c>
       <c r="O5" s="5">
         <v>39</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4137592529448363</v>
+        <v>0.4091637166054654</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3316670238850687</v>
+        <v>0.3227345088374806</v>
       </c>
       <c r="R5" s="5">
         <v>39</v>
@@ -2166,16 +2166,16 @@
         <v>3</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.142360667648442</v>
+        <v>-1.171974767690688</v>
       </c>
       <c r="O6" s="5">
         <v>39</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2943358739009098</v>
+        <v>0.2897292361165604</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3127471431573925</v>
+        <v>0.3119878072588734</v>
       </c>
       <c r="R6" s="5">
         <v>39</v>
@@ -2225,16 +2225,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.011616051095751</v>
+        <v>-1.027801962791816</v>
       </c>
       <c r="O7" s="5">
         <v>28</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5437884112375829</v>
+        <v>0.538705238817592</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4834545400597889</v>
+        <v>0.4812473804341121</v>
       </c>
       <c r="R7" s="5">
         <v>28</v>
@@ -2284,16 +2284,16 @@
         <v>2</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.520951452411276</v>
+        <v>-1.515533477409617</v>
       </c>
       <c r="O8" s="5">
         <v>16</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4186926801806889</v>
+        <v>0.4179534704828741</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.434398267124351</v>
+        <v>0.4339514802580264</v>
       </c>
       <c r="R8" s="5">
         <v>16</v>
@@ -2466,16 +2466,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3692327602179196</v>
+        <v>-0.3839276522058193</v>
       </c>
       <c r="O3" s="5">
         <v>47</v>
       </c>
       <c r="P3" s="4">
-        <v>0.168372575125227</v>
+        <v>0.1668096779181983</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1673476456284487</v>
+        <v>0.1660641525656939</v>
       </c>
       <c r="R3" s="5">
         <v>47</v>
@@ -2525,16 +2525,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1712169317077298</v>
+        <v>-0.2020304110677381</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1227843390821378</v>
+        <v>0.1189667359833799</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1230745647901931</v>
+        <v>0.1210975896183386</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -2584,16 +2584,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2035589854777135</v>
+        <v>-0.2475184498622547</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2798859022968563</v>
+        <v>0.2742905521066398</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.273926214262558</v>
+        <v>0.2689484416590208</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4363552352666134</v>
+        <v>-0.4083873996119942</v>
       </c>
       <c r="O6" s="5">
         <v>44</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1437028436994595</v>
+        <v>0.1434455022909229</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1226509910610527</v>
+        <v>0.1217521683556262</v>
       </c>
       <c r="R6" s="5">
         <v>44</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2256053229283404</v>
+        <v>-0.2264452132252438</v>
       </c>
       <c r="O7" s="5">
         <v>35</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1915481536903302</v>
+        <v>0.1914336231952979</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1351288845868397</v>
+        <v>0.1351048877212139</v>
       </c>
       <c r="R7" s="5">
         <v>35</v>
@@ -2761,16 +2761,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.3915042453071584</v>
+        <v>-0.5280040349228005</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2178631777897511</v>
+        <v>0.1996640081723033</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2178631777897511</v>
+        <v>0.1996640081723033</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -2943,16 +2943,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5983137379949834</v>
+        <v>-0.5649454069406523</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1835770875046185</v>
+        <v>0.1809815005170602</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1872399983804469</v>
+        <v>0.1813749642981714</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -3002,16 +3002,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.511893763266775</v>
+        <v>-0.4463598954822734</v>
       </c>
       <c r="O4" s="5">
         <v>41</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2070691214684806</v>
+        <v>0.2043916067336667</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.194850209685867</v>
+        <v>0.1917808635264461</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -3061,16 +3061,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4466788524325532</v>
+        <v>-0.4276007374309102</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1232410204504358</v>
+        <v>0.1216235855240434</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1239556427066542</v>
+        <v>0.1217943346034249</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -3120,16 +3120,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.7790792270936027</v>
+        <v>-0.6978226252820355</v>
       </c>
       <c r="O6" s="5">
         <v>44</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1768353872114973</v>
+        <v>0.1752225561572764</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1784516081064348</v>
+        <v>0.1749553808507187</v>
       </c>
       <c r="R6" s="5">
         <v>44</v>
@@ -3179,16 +3179,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5327197413329954</v>
+        <v>-0.5084918824139228</v>
       </c>
       <c r="O7" s="5">
         <v>33</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2611631383101298</v>
+        <v>0.26074980355625</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1958139852921594</v>
+        <v>0.1930603396579797</v>
       </c>
       <c r="R7" s="5">
         <v>33</v>
@@ -3238,16 +3238,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.8794218883250047</v>
+        <v>-0.8727164644292109</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2096831607283641</v>
+        <v>0.2092887240286115</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2096831607283641</v>
+        <v>0.2092887240286115</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -3420,16 +3420,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5455849983432167</v>
+        <v>-0.5771829301627716</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2608026348095768</v>
+        <v>0.2555702936344583</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2279988563225978</v>
+        <v>0.2251633870242463</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -3479,16 +3479,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2631214024031314</v>
+        <v>-0.2668279502101338</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09078650613944753</v>
+        <v>0.09024769357833014</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08503160827514399</v>
+        <v>0.08478746876015543</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -3538,16 +3538,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4607732051547211</v>
+        <v>-0.4728602378281328</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2302436333589973</v>
+        <v>0.2285236851385371</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1912333747569168</v>
+        <v>0.1902202732037032</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -3597,16 +3597,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5673705566853354</v>
+        <v>-0.5867923197951133</v>
       </c>
       <c r="O6" s="5">
         <v>43</v>
       </c>
       <c r="P6" s="4">
-        <v>0.177926607961923</v>
+        <v>0.1757708358112642</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1588750351395903</v>
+        <v>0.1575223323358673</v>
       </c>
       <c r="R6" s="5">
         <v>43</v>
@@ -3656,16 +3656,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4922069213887579</v>
+        <v>-0.5510468996580478</v>
       </c>
       <c r="O7" s="5">
         <v>34</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3367183493836611</v>
+        <v>0.3173660635765488</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2048067178903377</v>
+        <v>0.1936072840856724</v>
       </c>
       <c r="R7" s="5">
         <v>34</v>
@@ -3715,16 +3715,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.8109596567450559</v>
+        <v>-0.8512405788173242</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2345924312889635</v>
+        <v>0.2275544403487454</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2345924312889635</v>
+        <v>0.2275544403487454</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -3897,16 +3897,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6426294066039179</v>
+        <v>-0.6276406576029883</v>
       </c>
       <c r="O3" s="5">
         <v>48</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1897936963084764</v>
+        <v>0.1884948184407124</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1897936963084764</v>
+        <v>0.1884948184407124</v>
       </c>
       <c r="R3" s="5">
         <v>48</v>
@@ -3956,16 +3956,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.408701541167898</v>
+        <v>-0.4431928182348281</v>
       </c>
       <c r="O4" s="5">
         <v>47</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07369008460991988</v>
+        <v>0.07031309629436992</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07369008460991988</v>
+        <v>0.07031309629436992</v>
       </c>
       <c r="R4" s="5">
         <v>47</v>
@@ -4015,16 +4015,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4212879954042471</v>
+        <v>-0.4067297757717383</v>
       </c>
       <c r="O5" s="5">
         <v>47</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1617767061458946</v>
+        <v>0.1602683639503857</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1617767061458946</v>
+        <v>0.1602683639503857</v>
       </c>
       <c r="R5" s="5">
         <v>47</v>
@@ -4074,16 +4074,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.8482681759065318</v>
+        <v>-0.8946622732842382</v>
       </c>
       <c r="O6" s="5">
         <v>45</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1115159913680134</v>
+        <v>0.1060137475964691</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1115159913680134</v>
+        <v>0.1060137475964691</v>
       </c>
       <c r="R6" s="5">
         <v>45</v>
@@ -4133,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.7301202512472678</v>
+        <v>-0.8081872270234609</v>
       </c>
       <c r="O7" s="5">
         <v>36</v>
       </c>
       <c r="P7" s="4">
-        <v>0.224463485879946</v>
+        <v>0.2114566348208214</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1766286792128469</v>
+        <v>0.1650684710170386</v>
       </c>
       <c r="R7" s="5">
         <v>36</v>
@@ -4192,16 +4192,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.090896895999278</v>
+        <v>-1.128424446996758</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1281314266969151</v>
+        <v>0.1247152864154504</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1281314266969151</v>
+        <v>0.1247152864154504</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -4374,16 +4374,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1167499724393646</v>
+        <v>-0.08677743517094191</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.256191552038311</v>
+        <v>0.2562255394619579</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1955914827927978</v>
+        <v>0.1929037838669198</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -4433,16 +4433,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08477092318125273</v>
+        <v>-0.09076675879617227</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06130016405633793</v>
+        <v>0.06064088315912285</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05312612838766875</v>
+        <v>0.0528307034939335</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -4492,16 +4492,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2515596770605022</v>
+        <v>-0.1981403078427713</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2781415732535196</v>
+        <v>0.2786443915575998</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.229934649984607</v>
+        <v>0.2268295216354836</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -4551,16 +4551,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.0007481451180062858</v>
+        <v>0.04812951366686369</v>
       </c>
       <c r="O6" s="5">
         <v>44</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1124800132726102</v>
+        <v>0.1089648702587027</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1051553875033576</v>
+        <v>0.1004494989940233</v>
       </c>
       <c r="R6" s="5">
         <v>44</v>
@@ -4610,16 +4610,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.05661330721903306</v>
+        <v>-0.01904582959133216</v>
       </c>
       <c r="O7" s="5">
         <v>37</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1908948621613526</v>
+        <v>0.1900825920964453</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1527675922435784</v>
+        <v>0.14724198145808</v>
       </c>
       <c r="R7" s="5">
         <v>37</v>
@@ -4669,16 +4669,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.01720128310267179</v>
+        <v>-0.06151707094580872</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1514624535643973</v>
+        <v>0.1386759268001232</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1514624535643973</v>
+        <v>0.1386759268001232</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -4851,16 +4851,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7704240143003043</v>
+        <v>-0.8160688076784821</v>
       </c>
       <c r="O3" s="5">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1497167167520886</v>
+        <v>0.1357119204243312</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1497167167520886</v>
+        <v>0.1357119204243312</v>
       </c>
       <c r="R3" s="5">
         <v>25</v>
@@ -4910,16 +4910,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3915601590983965</v>
+        <v>-0.3814833337091721</v>
       </c>
       <c r="O4" s="5">
         <v>28</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06414406261806441</v>
+        <v>0.0634227731872761</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05907025469154748</v>
+        <v>0.05796331830290156</v>
       </c>
       <c r="R4" s="5">
         <v>28</v>
@@ -4969,16 +4969,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6808911740706763</v>
+        <v>-0.7169469814291506</v>
       </c>
       <c r="O5" s="5">
         <v>26</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3093731205131436</v>
+        <v>0.2972614559123692</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1782509957192718</v>
+        <v>0.1652076646107456</v>
       </c>
       <c r="R5" s="5">
         <v>26</v>
@@ -5028,16 +5028,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.8198779456508294</v>
+        <v>-0.8519906546097106</v>
       </c>
       <c r="O6" s="5">
         <v>25</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1031704368292961</v>
+        <v>0.100291927914311</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.08170566207198079</v>
+        <v>0.07999652115875153</v>
       </c>
       <c r="R6" s="5">
         <v>25</v>
@@ -5087,16 +5087,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.8709340100145074</v>
+        <v>-0.8834357813014667</v>
       </c>
       <c r="O7" s="5">
         <v>29</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1073834049118654</v>
+        <v>0.1042656232515049</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.08778606131080365</v>
+        <v>0.08531545134882931</v>
       </c>
       <c r="R7" s="5">
         <v>29</v>
@@ -5146,16 +5146,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.149353726003044</v>
+        <v>-1.257773963760086</v>
       </c>
       <c r="O8" s="5">
         <v>11</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1623477842727474</v>
+        <v>0.1505820985760154</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1623477842727474</v>
+        <v>0.1505820985760154</v>
       </c>
       <c r="R8" s="5">
         <v>11</v>
@@ -5328,16 +5328,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1053346253210952</v>
+        <v>-0.0821472463585485</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2352070947668654</v>
+        <v>0.2361839473968107</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.184130556006744</v>
+        <v>0.1830882698791801</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -5387,16 +5387,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.0851414202345725</v>
+        <v>-0.08971005040069116</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06268818238159043</v>
+        <v>0.06218860546747271</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0563010126531194</v>
+        <v>0.05607887118800173</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -5446,16 +5446,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2318937471271696</v>
+        <v>-0.1804303373685282</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.268647180531155</v>
+        <v>0.2697532356737714</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2222346183882954</v>
+        <v>0.2199072175343647</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -5505,16 +5505,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.005721403602499888</v>
+        <v>0.05535627844960195</v>
       </c>
       <c r="O6" s="5">
         <v>44</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1232992366374384</v>
+        <v>0.1185513660837341</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1166620629069862</v>
+        <v>0.1104181570667863</v>
       </c>
       <c r="R6" s="5">
         <v>44</v>
@@ -5564,16 +5564,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.04680349482202124</v>
+        <v>-0.02956910766283308</v>
       </c>
       <c r="O7" s="5">
         <v>36</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1923021660846673</v>
+        <v>0.1946523097881929</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1584037143109369</v>
+        <v>0.158403714310937</v>
       </c>
       <c r="R7" s="5">
         <v>36</v>
@@ -5623,16 +5623,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.05286982362951065</v>
+        <v>-0.02683261814623772</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.154301687587788</v>
+        <v>0.1313247420395474</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.154301687587788</v>
+        <v>0.1313247420395474</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -5769,13 +5769,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.1895609371654502</v>
+        <v>0.1855673168587504</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1696003315636369</v>
+        <v>0.1656893860163909</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1604266676659607</v>
+        <v>0.1593724475740311</v>
       </c>
       <c r="K3" s="4">
         <v>84.39927583936779</v>
@@ -5819,13 +5819,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2394210816311978</v>
+        <v>0.2327583995587439</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2093883928615733</v>
+        <v>0.2042869037727219</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2196177412357103</v>
+        <v>0.2168658242070112</v>
       </c>
       <c r="K4" s="4">
         <v>76.98472130787789</v>
@@ -5869,13 +5869,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1435095455299537</v>
+        <v>0.1353408681046483</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1246347213674834</v>
+        <v>0.1159670388216786</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1493833212724185</v>
+        <v>0.1432214208829397</v>
       </c>
       <c r="K5" s="4">
         <v>79.10508558261978</v>
@@ -5919,13 +5919,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2169189215879219</v>
+        <v>0.2144474059411915</v>
       </c>
       <c r="I6" s="4">
-        <v>0.187727891479589</v>
+        <v>0.1839237258790343</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2125789493694034</v>
+        <v>0.2041416032783368</v>
       </c>
       <c r="K6" s="4">
         <v>79.31232170287464</v>
@@ -5969,13 +5969,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1235811747808591</v>
+        <v>0.1217515091693274</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1031114927381785</v>
+        <v>0.1018118040141726</v>
       </c>
       <c r="J7" s="4">
-        <v>0.09576834730424615</v>
+        <v>0.09509913217318006</v>
       </c>
       <c r="K7" s="4">
         <v>83.78154487601485</v>
@@ -6019,13 +6019,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1835616936098166</v>
+        <v>0.180934484350448</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1363952672925121</v>
+        <v>0.1333790625858071</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1649637887907667</v>
+        <v>0.1612894996054308</v>
       </c>
       <c r="K8" s="4">
         <v>81.38742593811746</v>
@@ -6069,13 +6069,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.3600110351073317</v>
+        <v>0.357445446709006</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3383483889884761</v>
+        <v>0.3361187738102175</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3212847509719741</v>
+        <v>0.3195493218948786</v>
       </c>
       <c r="K9" s="4">
         <v>80.38073293833662</v>
@@ -6119,13 +6119,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1838943778310467</v>
+        <v>0.18049343646338</v>
       </c>
       <c r="I10" s="4">
-        <v>0.169537671915626</v>
+        <v>0.1664376414009117</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1711625961352542</v>
+        <v>0.169295188842313</v>
       </c>
       <c r="K10" s="4">
         <v>82.24393789774015</v>
@@ -6169,13 +6169,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1909260528748227</v>
+        <v>0.1892166965845568</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1773982637159622</v>
+        <v>0.1741228736811026</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1803309130267485</v>
+        <v>0.1719141415109838</v>
       </c>
       <c r="K11" s="4">
         <v>80.98762892253613</v>
@@ -6219,13 +6219,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2194246737514782</v>
+        <v>0.2136768096328648</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1772697936645159</v>
+        <v>0.1739878917422235</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1789539969459544</v>
+        <v>0.1747268496124077</v>
       </c>
       <c r="K12" s="4">
         <v>76.95317643186264</v>
@@ -6269,13 +6269,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1502011444857094</v>
+        <v>0.1454836708051517</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1405505121058367</v>
+        <v>0.1363263474340619</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1229462899835287</v>
+        <v>0.1278514551362156</v>
       </c>
       <c r="K13" s="4">
         <v>83.64466754443676</v>
@@ -6319,13 +6319,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1785757757837256</v>
+        <v>0.1768942652231744</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1474556485435571</v>
+        <v>0.1435566887875083</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1828444353933343</v>
+        <v>0.1817539047940163</v>
       </c>
       <c r="K14" s="4">
         <v>85.82194974764056</v>
@@ -6369,13 +6369,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1470845709728257</v>
+        <v>0.1403440448632702</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1139282909422198</v>
+        <v>0.1072335722596522</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1423539921885571</v>
+        <v>0.146292094926279</v>
       </c>
       <c r="K15" s="4">
         <v>80.97777777777814</v>
@@ -6419,13 +6419,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1753854526254478</v>
+        <v>0.1736698779347025</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1476685825424127</v>
+        <v>0.144073035018658</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1785527342531132</v>
+        <v>0.1775232534030108</v>
       </c>
       <c r="K16" s="4">
         <v>85.23137480798727</v>
@@ -8034,16 +8034,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6140422242410435</v>
+        <v>-0.5645960864353402</v>
       </c>
       <c r="O3" s="5">
         <v>48</v>
       </c>
       <c r="P3" s="4">
-        <v>0.186571702807763</v>
+        <v>0.1807971666087589</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.186571702807763</v>
+        <v>0.1807971666087589</v>
       </c>
       <c r="R3" s="5">
         <v>48</v>
@@ -8093,16 +8093,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.353702341848505</v>
+        <v>-0.3970220862970371</v>
       </c>
       <c r="O4" s="5">
         <v>47</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09262593081684253</v>
+        <v>0.08950894188872731</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09262593081684253</v>
+        <v>0.08950894188872731</v>
       </c>
       <c r="R4" s="5">
         <v>47</v>
@@ -8152,16 +8152,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.357150895494674</v>
+        <v>-0.3243478339614845</v>
       </c>
       <c r="O5" s="5">
         <v>45</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2596674898443894</v>
+        <v>0.2584727146657892</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2028871596727505</v>
+        <v>0.200181369529182</v>
       </c>
       <c r="R5" s="5">
         <v>45</v>
@@ -8211,13 +8211,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.790418022701906</v>
+        <v>-0.7836378140822149</v>
       </c>
       <c r="O6" s="5">
         <v>42</v>
       </c>
       <c r="P6" s="4">
-        <v>0.09292464255091952</v>
+        <v>0.09337665645889894</v>
       </c>
       <c r="Q6" s="4">
         <v>0.07557142458268748</v>
@@ -8270,16 +8270,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.9077506373194685</v>
+        <v>-0.9530753470056152</v>
       </c>
       <c r="O7" s="5">
         <v>38</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3017812221443546</v>
+        <v>0.2902685547999464</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2879451149167166</v>
+        <v>0.2793856800638385</v>
       </c>
       <c r="R7" s="5">
         <v>38</v>
@@ -8329,16 +8329,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.417932163512386</v>
+        <v>-1.390014760604731</v>
       </c>
       <c r="O8" s="5">
         <v>16</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2375233660022435</v>
+        <v>0.236089810225841</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2169363363295126</v>
+        <v>0.2136683456353564</v>
       </c>
       <c r="R8" s="5">
         <v>16</v>
@@ -8511,16 +8511,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6645774570335132</v>
+        <v>-0.6767033130837812</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2205662895333053</v>
+        <v>0.2186876109269742</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2052891990047164</v>
+        <v>0.2043420819841977</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -8570,16 +8570,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3735797496244788</v>
+        <v>-0.3887789884159375</v>
       </c>
       <c r="O4" s="5">
         <v>41</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1187520810694531</v>
+        <v>0.117083046334156</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1032273149071149</v>
+        <v>0.1020554574686747</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -8629,16 +8629,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.405890097951953</v>
+        <v>-0.4496069834921875</v>
       </c>
       <c r="O5" s="5">
         <v>42</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2966187280030061</v>
+        <v>0.2895170715467618</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2205313146666242</v>
+        <v>0.2177886140537119</v>
       </c>
       <c r="R5" s="5">
         <v>42</v>
@@ -8688,16 +8688,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.9868391320546586</v>
+        <v>-0.9893070009682025</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1385409266204578</v>
+        <v>0.1383764020262215</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1240523874165411</v>
+        <v>0.1240523874165412</v>
       </c>
       <c r="R6" s="5">
         <v>36</v>
@@ -8747,13 +8747,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.035463315295117</v>
+        <v>-1.101948198021687</v>
       </c>
       <c r="O7" s="5">
         <v>32</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3908026243674586</v>
+        <v>0.3847585441195884</v>
       </c>
       <c r="Q7" s="4">
         <v>0.3612478845567676</v>
@@ -8806,16 +8806,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.330174567364455</v>
+        <v>-1.484863990217437</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.343362420614356</v>
+        <v>0.2917975407781608</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.343362420614356</v>
+        <v>0.2917975407781608</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -8988,16 +8988,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4678319861899814</v>
+        <v>-0.5054958712677655</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1164768322184685</v>
+        <v>0.1036931225845356</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1119173840225058</v>
+        <v>0.09968351374356919</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -9047,16 +9047,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.213804037818985</v>
+        <v>-0.2710882238021907</v>
       </c>
       <c r="O4" s="5">
         <v>43</v>
       </c>
       <c r="P4" s="4">
-        <v>0.125381375437093</v>
+        <v>0.117032244961899</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1223038081658134</v>
+        <v>0.1091378355755368</v>
       </c>
       <c r="R4" s="5">
         <v>43</v>
@@ -9106,16 +9106,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3144529938769545</v>
+        <v>-0.3812203457547203</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1357253369446107</v>
+        <v>0.1259543280230644</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1236806217397431</v>
+        <v>0.1147608474798589</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -9165,16 +9165,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5794800660268105</v>
+        <v>-0.6181149389029579</v>
       </c>
       <c r="O6" s="5">
         <v>44</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1478120137870358</v>
+        <v>0.1419542838483195</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.146288438909806</v>
+        <v>0.13941951345257</v>
       </c>
       <c r="R6" s="5">
         <v>44</v>
@@ -9224,16 +9224,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4124154327093378</v>
+        <v>-0.4515188739606811</v>
       </c>
       <c r="O7" s="5">
         <v>34</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2081037845801373</v>
+        <v>0.2019413270744098</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1231183232732804</v>
+        <v>0.1191787660898227</v>
       </c>
       <c r="R7" s="5">
         <v>34</v>
@@ -9283,16 +9283,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.718572604163465</v>
+        <v>-0.7443940140693939</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1129033365329009</v>
+        <v>0.1113844300678463</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1129033365329009</v>
+        <v>0.1113844300678463</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -9465,16 +9465,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5341659621715636</v>
+        <v>-0.4917967660610351</v>
       </c>
       <c r="O3" s="5">
         <v>44</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2174215070762396</v>
+        <v>0.2105534700757655</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2092119274969017</v>
+        <v>0.2055712685973415</v>
       </c>
       <c r="R3" s="5">
         <v>44</v>
@@ -9524,16 +9524,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3267770779900731</v>
+        <v>-0.352150535163832</v>
       </c>
       <c r="O4" s="5">
         <v>41</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1492304208900516</v>
+        <v>0.148936939337211</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1288614452528272</v>
+        <v>0.1272872855618265</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -9583,16 +9583,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3464060029750735</v>
+        <v>-0.3332953174671953</v>
       </c>
       <c r="O5" s="5">
         <v>43</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2973927041664368</v>
+        <v>0.2960558684446692</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2638803033504866</v>
+        <v>0.2630289101433396</v>
       </c>
       <c r="R5" s="5">
         <v>43</v>
@@ -9642,16 +9642,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.7227549507689637</v>
+        <v>-0.7109814297401719</v>
       </c>
       <c r="O6" s="5">
         <v>43</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1515524298397479</v>
+        <v>0.1510743479597636</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1394996156431991</v>
+        <v>0.1389992973967039</v>
       </c>
       <c r="R6" s="5">
         <v>43</v>
@@ -9701,16 +9701,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5788046151167442</v>
+        <v>-0.5133874208693163</v>
       </c>
       <c r="O7" s="5">
         <v>21</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2741631665357187</v>
+        <v>0.2724771568953896</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1864673367212445</v>
+        <v>0.1673592226540245</v>
       </c>
       <c r="R7" s="5">
         <v>21</v>
@@ -9760,16 +9760,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7300725354322973</v>
+        <v>-0.6645222844229297</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2050196862429353</v>
+        <v>0.1984933872025809</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2050196862429353</v>
+        <v>0.1984933872025809</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
@@ -9942,16 +9942,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4578881692913476</v>
+        <v>-0.4614417405355242</v>
       </c>
       <c r="O3" s="5">
         <v>47</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1323256648779523</v>
+        <v>0.1319584576989276</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1219831803200562</v>
+        <v>0.1216837681211411</v>
       </c>
       <c r="R3" s="5">
         <v>47</v>
@@ -10001,16 +10001,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2313059660606379</v>
+        <v>-0.2265564604094102</v>
       </c>
       <c r="O4" s="5">
         <v>46</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06610334457985753</v>
+        <v>0.06603555143607968</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06389605459705469</v>
+        <v>0.06372353756642891</v>
       </c>
       <c r="R4" s="5">
         <v>46</v>
@@ -10060,16 +10060,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4075123728131878</v>
+        <v>-0.3689645242553359</v>
       </c>
       <c r="O5" s="5">
         <v>47</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1358370206036792</v>
+        <v>0.1348073347678458</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1358370206036792</v>
+        <v>0.1348073347678458</v>
       </c>
       <c r="R5" s="5">
         <v>47</v>
@@ -10119,16 +10119,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4191140409711466</v>
+        <v>-0.4050441251856875</v>
       </c>
       <c r="O6" s="5">
         <v>44</v>
       </c>
       <c r="P6" s="4">
-        <v>0.08500029579667751</v>
+        <v>0.08408311903007745</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.0744282436090833</v>
+        <v>0.07317045110266372</v>
       </c>
       <c r="R6" s="5">
         <v>44</v>
@@ -10178,16 +10178,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.362874313814085</v>
+        <v>-0.3856881717482226</v>
       </c>
       <c r="O7" s="5">
         <v>37</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2005976984855523</v>
+        <v>0.1936776644190341</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1095928209280108</v>
+        <v>0.1056797265121233</v>
       </c>
       <c r="R7" s="5">
         <v>37</v>
@@ -10237,16 +10237,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.5447004633246457</v>
+        <v>-0.5616401233166015</v>
       </c>
       <c r="O8" s="5">
         <v>17</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1267053072747257</v>
+        <v>0.1244232389452463</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1267053072747257</v>
+        <v>0.1244232389452463</v>
       </c>
       <c r="R8" s="5">
         <v>17</v>
